--- a/Quan Trac Lun/Phu Luc/PL KmKm117+200.xlsx
+++ b/Quan Trac Lun/Phu Luc/PL KmKm117+200.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Phu Luc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64D3E67B-ACA2-4896-81BD-93FE66B4C7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A219F2AC-18C9-44CE-BB90-1827A957CDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7792658D-355B-4513-A46A-F51BE949A234}"/>
   </bookViews>
@@ -2551,10 +2551,10 @@
                   <c:v>-8</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>-9</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>-10</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-11</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-11</c:v>
@@ -2563,10 +2563,10 @@
                   <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>-14</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>-15</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-16</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>-16</c:v>
@@ -2575,10 +2575,10 @@
                   <c:v>-18</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>-19</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>-20</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-21</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>-21</c:v>
@@ -2587,10 +2587,10 @@
                   <c:v>-23</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>-24</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>-25</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>-26</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>-26</c:v>
@@ -2749,31 +2749,31 @@
                   <c:v>-128</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>-131</c:v>
+                  <c:v>-130</c:v>
                 </c:pt>
                 <c:pt idx="82">
+                  <c:v>-132</c:v>
+                </c:pt>
+                <c:pt idx="83">
                   <c:v>-134</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>-137</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>-140</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>-143</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>-145</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>-147</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>-149</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="90">
                   <c:v>-150</c:v>
@@ -2959,10 +2959,10 @@
                   <c:v>-152</c:v>
                 </c:pt>
                 <c:pt idx="151">
+                  <c:v>-153</c:v>
+                </c:pt>
+                <c:pt idx="152">
                   <c:v>-154</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>-155</c:v>
                 </c:pt>
                 <c:pt idx="153">
                   <c:v>-155</c:v>
@@ -3451,49 +3451,49 @@
                   <c:v>-477</c:v>
                 </c:pt>
                 <c:pt idx="315">
-                  <c:v>-480</c:v>
+                  <c:v>-479</c:v>
                 </c:pt>
                 <c:pt idx="316">
+                  <c:v>-481</c:v>
+                </c:pt>
+                <c:pt idx="317">
                   <c:v>-483</c:v>
                 </c:pt>
-                <c:pt idx="317">
+                <c:pt idx="318">
                   <c:v>-486</c:v>
                 </c:pt>
-                <c:pt idx="318">
+                <c:pt idx="319">
                   <c:v>-489</c:v>
                 </c:pt>
-                <c:pt idx="319">
+                <c:pt idx="320">
                   <c:v>-492</c:v>
                 </c:pt>
-                <c:pt idx="320">
+                <c:pt idx="321">
                   <c:v>-495</c:v>
                 </c:pt>
-                <c:pt idx="321">
+                <c:pt idx="322">
                   <c:v>-498</c:v>
                 </c:pt>
-                <c:pt idx="322">
+                <c:pt idx="323">
                   <c:v>-501</c:v>
                 </c:pt>
-                <c:pt idx="323">
+                <c:pt idx="324">
                   <c:v>-504</c:v>
                 </c:pt>
-                <c:pt idx="324">
+                <c:pt idx="325">
                   <c:v>-507</c:v>
                 </c:pt>
-                <c:pt idx="325">
+                <c:pt idx="326">
                   <c:v>-509</c:v>
                 </c:pt>
-                <c:pt idx="326">
+                <c:pt idx="327">
                   <c:v>-511</c:v>
                 </c:pt>
-                <c:pt idx="327">
+                <c:pt idx="328">
                   <c:v>-513</c:v>
                 </c:pt>
-                <c:pt idx="328">
+                <c:pt idx="329">
                   <c:v>-515</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>-516</c:v>
                 </c:pt>
                 <c:pt idx="330">
                   <c:v>-516</c:v>
@@ -4183,16 +4183,16 @@
                   <c:v>-874</c:v>
                 </c:pt>
                 <c:pt idx="559">
-                  <c:v>-880</c:v>
+                  <c:v>-879</c:v>
                 </c:pt>
                 <c:pt idx="560">
-                  <c:v>-885</c:v>
+                  <c:v>-883</c:v>
                 </c:pt>
                 <c:pt idx="561">
-                  <c:v>-889</c:v>
+                  <c:v>-887</c:v>
                 </c:pt>
                 <c:pt idx="562">
-                  <c:v>-892</c:v>
+                  <c:v>-890</c:v>
                 </c:pt>
                 <c:pt idx="563">
                   <c:v>-892</c:v>
@@ -7476,172 +7476,172 @@
                   <c:v>-209</c:v>
                 </c:pt>
                 <c:pt idx="507">
-                  <c:v>-219</c:v>
+                  <c:v>-218</c:v>
                 </c:pt>
                 <c:pt idx="508">
-                  <c:v>-229</c:v>
+                  <c:v>-227</c:v>
                 </c:pt>
                 <c:pt idx="509">
-                  <c:v>-239</c:v>
+                  <c:v>-236</c:v>
                 </c:pt>
                 <c:pt idx="510">
-                  <c:v>-249</c:v>
+                  <c:v>-245</c:v>
                 </c:pt>
                 <c:pt idx="511">
-                  <c:v>-259</c:v>
+                  <c:v>-254</c:v>
                 </c:pt>
                 <c:pt idx="512">
-                  <c:v>-269</c:v>
+                  <c:v>-263</c:v>
                 </c:pt>
                 <c:pt idx="513">
-                  <c:v>-279</c:v>
+                  <c:v>-272</c:v>
                 </c:pt>
                 <c:pt idx="514">
-                  <c:v>-289</c:v>
+                  <c:v>-281</c:v>
                 </c:pt>
                 <c:pt idx="515">
+                  <c:v>-290</c:v>
+                </c:pt>
+                <c:pt idx="516">
                   <c:v>-299</c:v>
                 </c:pt>
-                <c:pt idx="516">
-                  <c:v>-309</c:v>
-                </c:pt>
                 <c:pt idx="517">
-                  <c:v>-319</c:v>
+                  <c:v>-308</c:v>
                 </c:pt>
                 <c:pt idx="518">
-                  <c:v>-329</c:v>
+                  <c:v>-317</c:v>
                 </c:pt>
                 <c:pt idx="519">
-                  <c:v>-339</c:v>
+                  <c:v>-326</c:v>
                 </c:pt>
                 <c:pt idx="520">
-                  <c:v>-349</c:v>
+                  <c:v>-335</c:v>
                 </c:pt>
                 <c:pt idx="521">
-                  <c:v>-359</c:v>
+                  <c:v>-344</c:v>
                 </c:pt>
                 <c:pt idx="522">
-                  <c:v>-369</c:v>
+                  <c:v>-353</c:v>
                 </c:pt>
                 <c:pt idx="523">
-                  <c:v>-379</c:v>
+                  <c:v>-362</c:v>
                 </c:pt>
                 <c:pt idx="524">
+                  <c:v>-371</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>-380</c:v>
+                </c:pt>
+                <c:pt idx="526">
                   <c:v>-389</c:v>
                 </c:pt>
-                <c:pt idx="525">
-                  <c:v>-399</c:v>
-                </c:pt>
-                <c:pt idx="526">
-                  <c:v>-409</c:v>
-                </c:pt>
                 <c:pt idx="527">
-                  <c:v>-419</c:v>
+                  <c:v>-398</c:v>
                 </c:pt>
                 <c:pt idx="528">
-                  <c:v>-429</c:v>
+                  <c:v>-407</c:v>
                 </c:pt>
                 <c:pt idx="529">
-                  <c:v>-439</c:v>
+                  <c:v>-416</c:v>
                 </c:pt>
                 <c:pt idx="530">
-                  <c:v>-449</c:v>
+                  <c:v>-425</c:v>
                 </c:pt>
                 <c:pt idx="531">
-                  <c:v>-459</c:v>
+                  <c:v>-434</c:v>
                 </c:pt>
                 <c:pt idx="532">
-                  <c:v>-469</c:v>
+                  <c:v>-443</c:v>
                 </c:pt>
                 <c:pt idx="533">
+                  <c:v>-452</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>-461</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>-470</c:v>
+                </c:pt>
+                <c:pt idx="536">
                   <c:v>-479</c:v>
                 </c:pt>
-                <c:pt idx="534">
-                  <c:v>-489</c:v>
-                </c:pt>
-                <c:pt idx="535">
-                  <c:v>-499</c:v>
-                </c:pt>
-                <c:pt idx="536">
-                  <c:v>-509</c:v>
-                </c:pt>
                 <c:pt idx="537">
-                  <c:v>-519</c:v>
+                  <c:v>-488</c:v>
                 </c:pt>
                 <c:pt idx="538">
-                  <c:v>-529</c:v>
+                  <c:v>-497</c:v>
                 </c:pt>
                 <c:pt idx="539">
-                  <c:v>-539</c:v>
+                  <c:v>-506</c:v>
                 </c:pt>
                 <c:pt idx="540">
-                  <c:v>-549</c:v>
+                  <c:v>-515</c:v>
                 </c:pt>
                 <c:pt idx="541">
-                  <c:v>-559</c:v>
+                  <c:v>-524</c:v>
                 </c:pt>
                 <c:pt idx="542">
+                  <c:v>-533</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>-542</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>-551</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>-560</c:v>
+                </c:pt>
+                <c:pt idx="546">
                   <c:v>-569</c:v>
                 </c:pt>
-                <c:pt idx="543">
-                  <c:v>-579</c:v>
-                </c:pt>
-                <c:pt idx="544">
-                  <c:v>-588</c:v>
-                </c:pt>
-                <c:pt idx="545">
+                <c:pt idx="547">
+                  <c:v>-578</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>-587</c:v>
+                </c:pt>
+                <c:pt idx="549">
                   <c:v>-597</c:v>
                 </c:pt>
-                <c:pt idx="546">
-                  <c:v>-606</c:v>
-                </c:pt>
-                <c:pt idx="547">
-                  <c:v>-615</c:v>
-                </c:pt>
-                <c:pt idx="548">
-                  <c:v>-624</c:v>
-                </c:pt>
-                <c:pt idx="549">
-                  <c:v>-632</c:v>
-                </c:pt>
                 <c:pt idx="550">
-                  <c:v>-640</c:v>
+                  <c:v>-607</c:v>
                 </c:pt>
                 <c:pt idx="551">
-                  <c:v>-648</c:v>
+                  <c:v>-617</c:v>
                 </c:pt>
                 <c:pt idx="552">
+                  <c:v>-627</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>-637</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>-647</c:v>
+                </c:pt>
+                <c:pt idx="555">
                   <c:v>-656</c:v>
                 </c:pt>
-                <c:pt idx="553">
-                  <c:v>-664</c:v>
-                </c:pt>
-                <c:pt idx="554">
-                  <c:v>-672</c:v>
-                </c:pt>
-                <c:pt idx="555">
-                  <c:v>-679</c:v>
-                </c:pt>
                 <c:pt idx="556">
-                  <c:v>-686</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="557">
-                  <c:v>-692</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="558">
-                  <c:v>-698</c:v>
+                  <c:v>-682</c:v>
                 </c:pt>
                 <c:pt idx="559">
+                  <c:v>-690</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>-697</c:v>
+                </c:pt>
+                <c:pt idx="561">
                   <c:v>-703</c:v>
                 </c:pt>
-                <c:pt idx="560">
-                  <c:v>-707</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>-710</c:v>
-                </c:pt>
                 <c:pt idx="562">
-                  <c:v>-711</c:v>
+                  <c:v>-708</c:v>
                 </c:pt>
                 <c:pt idx="563">
                   <c:v>-711</c:v>
@@ -11069,22 +11069,22 @@
                   <c:v>-441</c:v>
                 </c:pt>
                 <c:pt idx="556">
-                  <c:v>-446</c:v>
+                  <c:v>-445</c:v>
                 </c:pt>
                 <c:pt idx="557">
-                  <c:v>-451</c:v>
+                  <c:v>-449</c:v>
                 </c:pt>
                 <c:pt idx="558">
-                  <c:v>-455</c:v>
+                  <c:v>-453</c:v>
                 </c:pt>
                 <c:pt idx="559">
+                  <c:v>-456</c:v>
+                </c:pt>
+                <c:pt idx="560">
                   <c:v>-459</c:v>
                 </c:pt>
-                <c:pt idx="560">
+                <c:pt idx="561">
                   <c:v>-461</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>-462</c:v>
                 </c:pt>
                 <c:pt idx="562">
                   <c:v>-462</c:v>
@@ -14374,172 +14374,172 @@
                   <c:v>1.2909999999999999</c:v>
                 </c:pt>
                 <c:pt idx="507">
-                  <c:v>1.2809999999999999</c:v>
+                  <c:v>1.282</c:v>
                 </c:pt>
                 <c:pt idx="508">
-                  <c:v>1.2709999999999999</c:v>
+                  <c:v>1.2729999999999999</c:v>
                 </c:pt>
                 <c:pt idx="509">
-                  <c:v>1.2609999999999999</c:v>
+                  <c:v>1.264</c:v>
                 </c:pt>
                 <c:pt idx="510">
-                  <c:v>1.2509999999999999</c:v>
+                  <c:v>1.2549999999999999</c:v>
                 </c:pt>
                 <c:pt idx="511">
-                  <c:v>1.2410000000000001</c:v>
+                  <c:v>1.246</c:v>
                 </c:pt>
                 <c:pt idx="512">
-                  <c:v>1.2310000000000001</c:v>
+                  <c:v>1.2370000000000001</c:v>
                 </c:pt>
                 <c:pt idx="513">
-                  <c:v>1.2210000000000001</c:v>
+                  <c:v>1.228</c:v>
                 </c:pt>
                 <c:pt idx="514">
-                  <c:v>1.2110000000000001</c:v>
+                  <c:v>1.2190000000000001</c:v>
                 </c:pt>
                 <c:pt idx="515">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="516">
                   <c:v>1.2010000000000001</c:v>
                 </c:pt>
-                <c:pt idx="516">
-                  <c:v>1.1910000000000001</c:v>
-                </c:pt>
                 <c:pt idx="517">
-                  <c:v>1.181</c:v>
+                  <c:v>1.1919999999999999</c:v>
                 </c:pt>
                 <c:pt idx="518">
-                  <c:v>1.171</c:v>
+                  <c:v>1.1830000000000001</c:v>
                 </c:pt>
                 <c:pt idx="519">
-                  <c:v>1.161</c:v>
+                  <c:v>1.1739999999999999</c:v>
                 </c:pt>
                 <c:pt idx="520">
-                  <c:v>1.151</c:v>
+                  <c:v>1.165</c:v>
                 </c:pt>
                 <c:pt idx="521">
-                  <c:v>1.141</c:v>
+                  <c:v>1.1559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="522">
-                  <c:v>1.131</c:v>
+                  <c:v>1.147</c:v>
                 </c:pt>
                 <c:pt idx="523">
-                  <c:v>1.121</c:v>
+                  <c:v>1.1379999999999999</c:v>
                 </c:pt>
                 <c:pt idx="524">
+                  <c:v>1.129</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="526">
                   <c:v>1.111</c:v>
                 </c:pt>
-                <c:pt idx="525">
-                  <c:v>1.101</c:v>
-                </c:pt>
-                <c:pt idx="526">
-                  <c:v>1.091</c:v>
-                </c:pt>
                 <c:pt idx="527">
-                  <c:v>1.081</c:v>
+                  <c:v>1.1020000000000001</c:v>
                 </c:pt>
                 <c:pt idx="528">
-                  <c:v>1.071</c:v>
+                  <c:v>1.093</c:v>
                 </c:pt>
                 <c:pt idx="529">
-                  <c:v>1.0609999999999999</c:v>
+                  <c:v>1.0840000000000001</c:v>
                 </c:pt>
                 <c:pt idx="530">
-                  <c:v>1.0509999999999999</c:v>
+                  <c:v>1.075</c:v>
                 </c:pt>
                 <c:pt idx="531">
-                  <c:v>1.0409999999999999</c:v>
+                  <c:v>1.0660000000000001</c:v>
                 </c:pt>
                 <c:pt idx="532">
-                  <c:v>1.0309999999999999</c:v>
+                  <c:v>1.0569999999999999</c:v>
                 </c:pt>
                 <c:pt idx="533">
+                  <c:v>1.048</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.0389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="536">
                   <c:v>1.0209999999999999</c:v>
                 </c:pt>
-                <c:pt idx="534">
-                  <c:v>1.0109999999999999</c:v>
-                </c:pt>
-                <c:pt idx="535">
-                  <c:v>1.0009999999999999</c:v>
-                </c:pt>
-                <c:pt idx="536">
-                  <c:v>0.99099999999999999</c:v>
-                </c:pt>
                 <c:pt idx="537">
-                  <c:v>0.98099999999999998</c:v>
+                  <c:v>1.012</c:v>
                 </c:pt>
                 <c:pt idx="538">
-                  <c:v>0.97099999999999997</c:v>
+                  <c:v>1.0029999999999999</c:v>
                 </c:pt>
                 <c:pt idx="539">
-                  <c:v>0.96099999999999997</c:v>
+                  <c:v>0.99399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="540">
-                  <c:v>0.95099999999999996</c:v>
+                  <c:v>0.98499999999999999</c:v>
                 </c:pt>
                 <c:pt idx="541">
-                  <c:v>0.94099999999999995</c:v>
+                  <c:v>0.97599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="542">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>0.95799999999999996</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>0.94899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="546">
                   <c:v>0.93100000000000005</c:v>
                 </c:pt>
-                <c:pt idx="543">
-                  <c:v>0.92100000000000004</c:v>
-                </c:pt>
-                <c:pt idx="544">
-                  <c:v>0.91200000000000003</c:v>
-                </c:pt>
-                <c:pt idx="545">
+                <c:pt idx="547">
+                  <c:v>0.92200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>0.91300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="549">
                   <c:v>0.90300000000000002</c:v>
                 </c:pt>
-                <c:pt idx="546">
-                  <c:v>0.89400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="547">
-                  <c:v>0.88500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="548">
-                  <c:v>0.876</c:v>
-                </c:pt>
-                <c:pt idx="549">
-                  <c:v>0.86799999999999999</c:v>
-                </c:pt>
                 <c:pt idx="550">
-                  <c:v>0.86</c:v>
+                  <c:v>0.89300000000000002</c:v>
                 </c:pt>
                 <c:pt idx="551">
-                  <c:v>0.85199999999999998</c:v>
+                  <c:v>0.88300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="552">
+                  <c:v>0.873</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>0.86299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>0.85299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="555">
                   <c:v>0.84399999999999997</c:v>
                 </c:pt>
-                <c:pt idx="553">
-                  <c:v>0.83599999999999997</c:v>
-                </c:pt>
-                <c:pt idx="554">
-                  <c:v>0.82799999999999996</c:v>
-                </c:pt>
-                <c:pt idx="555">
-                  <c:v>0.82099999999999995</c:v>
-                </c:pt>
                 <c:pt idx="556">
-                  <c:v>0.81399999999999995</c:v>
+                  <c:v>0.83499999999999996</c:v>
                 </c:pt>
                 <c:pt idx="557">
-                  <c:v>0.80800000000000005</c:v>
+                  <c:v>0.82599999999999996</c:v>
                 </c:pt>
                 <c:pt idx="558">
-                  <c:v>0.80200000000000005</c:v>
+                  <c:v>0.81799999999999995</c:v>
                 </c:pt>
                 <c:pt idx="559">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>0.80300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="561">
                   <c:v>0.79700000000000004</c:v>
                 </c:pt>
-                <c:pt idx="560">
-                  <c:v>0.79300000000000004</c:v>
-                </c:pt>
-                <c:pt idx="561">
-                  <c:v>0.79</c:v>
-                </c:pt>
                 <c:pt idx="562">
-                  <c:v>0.78900000000000003</c:v>
+                  <c:v>0.79200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="563">
                   <c:v>0.78900000000000003</c:v>
@@ -19581,10 +19581,10 @@
         <v>0.5</v>
       </c>
       <c r="E28" s="33">
-        <v>1.29</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="F28" s="33">
-        <v>-0.71</v>
+        <v>-0.70899999999999996</v>
       </c>
       <c r="G28" s="33">
         <v>1.2949999999999999</v>
@@ -19599,7 +19599,7 @@
         <v>-0.70499999999999996</v>
       </c>
       <c r="K28" s="32">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L28" s="35">
         <v>-5</v>
@@ -19623,10 +19623,10 @@
         <v>0.5</v>
       </c>
       <c r="E29" s="33">
-        <v>1.2889999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="F29" s="33">
-        <v>-0.71099999999999997</v>
+        <v>-0.71</v>
       </c>
       <c r="G29" s="33">
         <v>1.294</v>
@@ -19641,7 +19641,7 @@
         <v>-0.70499999999999996</v>
       </c>
       <c r="K29" s="32">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L29" s="35">
         <v>-6</v>
@@ -19749,10 +19749,10 @@
         <v>0.8</v>
       </c>
       <c r="E32" s="33">
-        <v>1.2849999999999999</v>
+        <v>1.286</v>
       </c>
       <c r="F32" s="33">
-        <v>-0.71499999999999997</v>
+        <v>-0.71399999999999997</v>
       </c>
       <c r="G32" s="33">
         <v>1.292</v>
@@ -19767,7 +19767,7 @@
         <v>-0.70699999999999996</v>
       </c>
       <c r="K32" s="32">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L32" s="35">
         <v>-8</v>
@@ -19791,10 +19791,10 @@
         <v>0.8</v>
       </c>
       <c r="E33" s="33">
-        <v>1.284</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="F33" s="33">
-        <v>-0.71599999999999997</v>
+        <v>-0.71499999999999997</v>
       </c>
       <c r="G33" s="33">
         <v>1.2909999999999999</v>
@@ -19809,7 +19809,7 @@
         <v>-0.70699999999999996</v>
       </c>
       <c r="K33" s="32">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L33" s="35">
         <v>-9</v>
@@ -19917,10 +19917,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E36" s="33">
-        <v>1.28</v>
+        <v>1.2809999999999999</v>
       </c>
       <c r="F36" s="33">
-        <v>-0.72</v>
+        <v>-0.71899999999999997</v>
       </c>
       <c r="G36" s="33">
         <v>1.2889999999999999</v>
@@ -19935,7 +19935,7 @@
         <v>-0.70899999999999996</v>
       </c>
       <c r="K36" s="32">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L36" s="35">
         <v>-11</v>
@@ -19959,10 +19959,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E37" s="33">
-        <v>1.2789999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="F37" s="33">
-        <v>-0.72099999999999997</v>
+        <v>-0.72</v>
       </c>
       <c r="G37" s="33">
         <v>1.288</v>
@@ -19977,7 +19977,7 @@
         <v>-0.70899999999999996</v>
       </c>
       <c r="K37" s="32">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="L37" s="35">
         <v>-12</v>
@@ -20085,10 +20085,10 @@
         <v>1.4</v>
       </c>
       <c r="E40" s="33">
-        <v>1.2749999999999999</v>
+        <v>1.276</v>
       </c>
       <c r="F40" s="33">
-        <v>-0.72499999999999998</v>
+        <v>-0.72399999999999998</v>
       </c>
       <c r="G40" s="33">
         <v>1.286</v>
@@ -20103,7 +20103,7 @@
         <v>-0.71099999999999997</v>
       </c>
       <c r="K40" s="32">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="L40" s="35">
         <v>-14</v>
@@ -20127,10 +20127,10 @@
         <v>1.4</v>
       </c>
       <c r="E41" s="33">
-        <v>1.274</v>
+        <v>1.2749999999999999</v>
       </c>
       <c r="F41" s="33">
-        <v>-0.72599999999999998</v>
+        <v>-0.72499999999999998</v>
       </c>
       <c r="G41" s="33">
         <v>1.2849999999999999</v>
@@ -20145,7 +20145,7 @@
         <v>-0.71099999999999997</v>
       </c>
       <c r="K41" s="32">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="L41" s="35">
         <v>-15</v>
@@ -22353,10 +22353,10 @@
         <v>1.7</v>
       </c>
       <c r="E94" s="33">
-        <v>1.169</v>
+        <v>1.17</v>
       </c>
       <c r="F94" s="33">
-        <v>-0.83099999999999996</v>
+        <v>-0.83</v>
       </c>
       <c r="G94" s="33">
         <v>1.236</v>
@@ -22371,7 +22371,7 @@
         <v>-0.746</v>
       </c>
       <c r="K94" s="32">
-        <v>-131</v>
+        <v>-130</v>
       </c>
       <c r="L94" s="35">
         <v>-64</v>
@@ -22395,10 +22395,10 @@
         <v>1.7</v>
       </c>
       <c r="E95" s="33">
-        <v>1.1659999999999999</v>
+        <v>1.1679999999999999</v>
       </c>
       <c r="F95" s="33">
-        <v>-0.83399999999999996</v>
+        <v>-0.83199999999999996</v>
       </c>
       <c r="G95" s="33">
         <v>1.236</v>
@@ -22413,7 +22413,7 @@
         <v>-0.746</v>
       </c>
       <c r="K95" s="32">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="L95" s="35">
         <v>-64</v>
@@ -22437,10 +22437,10 @@
         <v>1.7</v>
       </c>
       <c r="E96" s="33">
-        <v>1.163</v>
+        <v>1.1659999999999999</v>
       </c>
       <c r="F96" s="33">
-        <v>-0.83699999999999997</v>
+        <v>-0.83399999999999996</v>
       </c>
       <c r="G96" s="33">
         <v>1.236</v>
@@ -22455,7 +22455,7 @@
         <v>-0.746</v>
       </c>
       <c r="K96" s="32">
-        <v>-137</v>
+        <v>-134</v>
       </c>
       <c r="L96" s="35">
         <v>-64</v>
@@ -22479,10 +22479,10 @@
         <v>1.7</v>
       </c>
       <c r="E97" s="33">
-        <v>1.1599999999999999</v>
+        <v>1.163</v>
       </c>
       <c r="F97" s="33">
-        <v>-0.84</v>
+        <v>-0.83699999999999997</v>
       </c>
       <c r="G97" s="33">
         <v>1.236</v>
@@ -22497,7 +22497,7 @@
         <v>-0.746</v>
       </c>
       <c r="K97" s="32">
-        <v>-140</v>
+        <v>-137</v>
       </c>
       <c r="L97" s="35">
         <v>-64</v>
@@ -22521,10 +22521,10 @@
         <v>1.7</v>
       </c>
       <c r="E98" s="33">
-        <v>1.157</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="F98" s="33">
-        <v>-0.84299999999999997</v>
+        <v>-0.84</v>
       </c>
       <c r="G98" s="33">
         <v>1.236</v>
@@ -22539,7 +22539,7 @@
         <v>-0.746</v>
       </c>
       <c r="K98" s="32">
-        <v>-143</v>
+        <v>-140</v>
       </c>
       <c r="L98" s="35">
         <v>-64</v>
@@ -22563,10 +22563,10 @@
         <v>1.7</v>
       </c>
       <c r="E99" s="33">
-        <v>1.155</v>
+        <v>1.157</v>
       </c>
       <c r="F99" s="33">
-        <v>-0.84499999999999997</v>
+        <v>-0.84299999999999997</v>
       </c>
       <c r="G99" s="33">
         <v>1.236</v>
@@ -22581,7 +22581,7 @@
         <v>-0.746</v>
       </c>
       <c r="K99" s="32">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="L99" s="35">
         <v>-64</v>
@@ -22605,10 +22605,10 @@
         <v>1.7</v>
       </c>
       <c r="E100" s="33">
-        <v>1.153</v>
+        <v>1.155</v>
       </c>
       <c r="F100" s="33">
-        <v>-0.84699999999999998</v>
+        <v>-0.84499999999999997</v>
       </c>
       <c r="G100" s="33">
         <v>1.236</v>
@@ -22623,7 +22623,7 @@
         <v>-0.746</v>
       </c>
       <c r="K100" s="32">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="L100" s="35">
         <v>-64</v>
@@ -22647,10 +22647,10 @@
         <v>1.7</v>
       </c>
       <c r="E101" s="33">
-        <v>1.151</v>
+        <v>1.153</v>
       </c>
       <c r="F101" s="33">
-        <v>-0.84899999999999998</v>
+        <v>-0.84699999999999998</v>
       </c>
       <c r="G101" s="33">
         <v>1.236</v>
@@ -22665,7 +22665,7 @@
         <v>-0.746</v>
       </c>
       <c r="K101" s="32">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="L101" s="35">
         <v>-64</v>
@@ -22689,10 +22689,10 @@
         <v>1.7</v>
       </c>
       <c r="E102" s="33">
-        <v>1.1499999999999999</v>
+        <v>1.151</v>
       </c>
       <c r="F102" s="33">
-        <v>-0.85</v>
+        <v>-0.84899999999999998</v>
       </c>
       <c r="G102" s="33">
         <v>1.236</v>
@@ -22707,7 +22707,7 @@
         <v>-0.746</v>
       </c>
       <c r="K102" s="32">
-        <v>-150</v>
+        <v>-149</v>
       </c>
       <c r="L102" s="35">
         <v>-64</v>
@@ -25293,10 +25293,10 @@
         <v>2</v>
       </c>
       <c r="E164" s="33">
-        <v>1.1459999999999999</v>
+        <v>1.147</v>
       </c>
       <c r="F164" s="33">
-        <v>-0.85399999999999998</v>
+        <v>-0.85299999999999998</v>
       </c>
       <c r="G164" s="33">
         <v>1.234</v>
@@ -25311,7 +25311,7 @@
         <v>-0.748</v>
       </c>
       <c r="K164" s="32">
-        <v>-154</v>
+        <v>-153</v>
       </c>
       <c r="L164" s="35">
         <v>-66</v>
@@ -25335,10 +25335,10 @@
         <v>2</v>
       </c>
       <c r="E165" s="33">
-        <v>1.145</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="F165" s="33">
-        <v>-0.85499999999999998</v>
+        <v>-0.85399999999999998</v>
       </c>
       <c r="G165" s="33">
         <v>1.234</v>
@@ -25353,7 +25353,7 @@
         <v>-0.748</v>
       </c>
       <c r="K165" s="32">
-        <v>-155</v>
+        <v>-154</v>
       </c>
       <c r="L165" s="35">
         <v>-66</v>
@@ -32181,10 +32181,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E328" s="33">
-        <v>0.82</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="F328" s="33">
-        <v>-1.18</v>
+        <v>-1.179</v>
       </c>
       <c r="G328" s="33">
         <v>1.091</v>
@@ -32199,7 +32199,7 @@
         <v>-0.85</v>
       </c>
       <c r="K328" s="32">
-        <v>-480</v>
+        <v>-479</v>
       </c>
       <c r="L328" s="35">
         <v>-209</v>
@@ -32223,10 +32223,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E329" s="33">
-        <v>0.81699999999999995</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="F329" s="33">
-        <v>-1.1830000000000001</v>
+        <v>-1.181</v>
       </c>
       <c r="G329" s="33">
         <v>1.091</v>
@@ -32241,7 +32241,7 @@
         <v>-0.85</v>
       </c>
       <c r="K329" s="32">
-        <v>-483</v>
+        <v>-481</v>
       </c>
       <c r="L329" s="35">
         <v>-209</v>
@@ -32265,10 +32265,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E330" s="33">
-        <v>0.81399999999999995</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="F330" s="33">
-        <v>-1.1859999999999999</v>
+        <v>-1.1830000000000001</v>
       </c>
       <c r="G330" s="33">
         <v>1.091</v>
@@ -32283,7 +32283,7 @@
         <v>-0.85</v>
       </c>
       <c r="K330" s="32">
-        <v>-486</v>
+        <v>-483</v>
       </c>
       <c r="L330" s="35">
         <v>-209</v>
@@ -32307,10 +32307,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E331" s="33">
-        <v>0.81100000000000005</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="F331" s="33">
-        <v>-1.1890000000000001</v>
+        <v>-1.1859999999999999</v>
       </c>
       <c r="G331" s="33">
         <v>1.091</v>
@@ -32325,7 +32325,7 @@
         <v>-0.85</v>
       </c>
       <c r="K331" s="32">
-        <v>-489</v>
+        <v>-486</v>
       </c>
       <c r="L331" s="35">
         <v>-209</v>
@@ -32349,10 +32349,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E332" s="33">
-        <v>0.80800000000000005</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="F332" s="33">
-        <v>-1.1919999999999999</v>
+        <v>-1.1890000000000001</v>
       </c>
       <c r="G332" s="33">
         <v>1.091</v>
@@ -32367,7 +32367,7 @@
         <v>-0.85</v>
       </c>
       <c r="K332" s="32">
-        <v>-492</v>
+        <v>-489</v>
       </c>
       <c r="L332" s="35">
         <v>-209</v>
@@ -32391,10 +32391,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E333" s="33">
-        <v>0.80500000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F333" s="33">
-        <v>-1.1950000000000001</v>
+        <v>-1.1919999999999999</v>
       </c>
       <c r="G333" s="33">
         <v>1.091</v>
@@ -32409,7 +32409,7 @@
         <v>-0.85</v>
       </c>
       <c r="K333" s="32">
-        <v>-495</v>
+        <v>-492</v>
       </c>
       <c r="L333" s="35">
         <v>-209</v>
@@ -32433,10 +32433,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E334" s="33">
-        <v>0.80200000000000005</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="F334" s="33">
-        <v>-1.198</v>
+        <v>-1.1950000000000001</v>
       </c>
       <c r="G334" s="33">
         <v>1.091</v>
@@ -32451,7 +32451,7 @@
         <v>-0.85</v>
       </c>
       <c r="K334" s="32">
-        <v>-498</v>
+        <v>-495</v>
       </c>
       <c r="L334" s="35">
         <v>-209</v>
@@ -32475,10 +32475,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E335" s="33">
-        <v>0.79900000000000004</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="F335" s="33">
-        <v>-1.2010000000000001</v>
+        <v>-1.198</v>
       </c>
       <c r="G335" s="33">
         <v>1.091</v>
@@ -32493,7 +32493,7 @@
         <v>-0.85</v>
       </c>
       <c r="K335" s="32">
-        <v>-501</v>
+        <v>-498</v>
       </c>
       <c r="L335" s="35">
         <v>-209</v>
@@ -32517,10 +32517,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E336" s="33">
-        <v>0.79600000000000004</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="F336" s="33">
-        <v>-1.204</v>
+        <v>-1.2010000000000001</v>
       </c>
       <c r="G336" s="33">
         <v>1.091</v>
@@ -32535,7 +32535,7 @@
         <v>-0.85</v>
       </c>
       <c r="K336" s="32">
-        <v>-504</v>
+        <v>-501</v>
       </c>
       <c r="L336" s="35">
         <v>-209</v>
@@ -32559,10 +32559,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E337" s="33">
-        <v>0.79300000000000004</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="F337" s="33">
-        <v>-1.2070000000000001</v>
+        <v>-1.204</v>
       </c>
       <c r="G337" s="33">
         <v>1.091</v>
@@ -32577,7 +32577,7 @@
         <v>-0.85</v>
       </c>
       <c r="K337" s="32">
-        <v>-507</v>
+        <v>-504</v>
       </c>
       <c r="L337" s="35">
         <v>-209</v>
@@ -32601,10 +32601,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E338" s="33">
-        <v>0.79100000000000004</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="F338" s="33">
-        <v>-1.2090000000000001</v>
+        <v>-1.2070000000000001</v>
       </c>
       <c r="G338" s="33">
         <v>1.091</v>
@@ -32619,7 +32619,7 @@
         <v>-0.85</v>
       </c>
       <c r="K338" s="32">
-        <v>-509</v>
+        <v>-507</v>
       </c>
       <c r="L338" s="35">
         <v>-209</v>
@@ -32643,10 +32643,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E339" s="33">
-        <v>0.78900000000000003</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="F339" s="33">
-        <v>-1.2110000000000001</v>
+        <v>-1.2090000000000001</v>
       </c>
       <c r="G339" s="33">
         <v>1.091</v>
@@ -32661,7 +32661,7 @@
         <v>-0.85</v>
       </c>
       <c r="K339" s="32">
-        <v>-511</v>
+        <v>-509</v>
       </c>
       <c r="L339" s="35">
         <v>-209</v>
@@ -32685,10 +32685,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E340" s="33">
-        <v>0.78700000000000003</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="F340" s="33">
-        <v>-1.2130000000000001</v>
+        <v>-1.2110000000000001</v>
       </c>
       <c r="G340" s="33">
         <v>1.091</v>
@@ -32703,7 +32703,7 @@
         <v>-0.85</v>
       </c>
       <c r="K340" s="32">
-        <v>-513</v>
+        <v>-511</v>
       </c>
       <c r="L340" s="35">
         <v>-209</v>
@@ -32727,10 +32727,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E341" s="33">
-        <v>0.78500000000000003</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="F341" s="33">
-        <v>-1.2150000000000001</v>
+        <v>-1.2130000000000001</v>
       </c>
       <c r="G341" s="33">
         <v>1.091</v>
@@ -32745,7 +32745,7 @@
         <v>-0.85</v>
       </c>
       <c r="K341" s="32">
-        <v>-515</v>
+        <v>-513</v>
       </c>
       <c r="L341" s="35">
         <v>-209</v>
@@ -32769,10 +32769,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E342" s="33">
-        <v>0.78400000000000003</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="F342" s="33">
-        <v>-1.216</v>
+        <v>-1.2150000000000001</v>
       </c>
       <c r="G342" s="33">
         <v>1.091</v>
@@ -32787,7 +32787,7 @@
         <v>-0.85</v>
       </c>
       <c r="K342" s="32">
-        <v>-516</v>
+        <v>-515</v>
       </c>
       <c r="L342" s="35">
         <v>-209</v>
@@ -40239,7 +40239,7 @@
         <v>507</v>
       </c>
       <c r="C520" s="33">
-        <v>1.2809999999999999</v>
+        <v>1.282</v>
       </c>
       <c r="D520" s="34">
         <v>2.2000000000000002</v>
@@ -40251,10 +40251,10 @@
         <v>-1.2230000000000001</v>
       </c>
       <c r="G520" s="33">
-        <v>1.081</v>
+        <v>1.0820000000000001</v>
       </c>
       <c r="H520" s="33">
-        <v>-0.91900000000000004</v>
+        <v>-0.91800000000000004</v>
       </c>
       <c r="I520" s="33">
         <v>1.1439999999999999</v>
@@ -40266,7 +40266,7 @@
         <v>-523</v>
       </c>
       <c r="L520" s="35">
-        <v>-219</v>
+        <v>-218</v>
       </c>
       <c r="M520" s="32">
         <v>-156</v>
@@ -40281,7 +40281,7 @@
         <v>508</v>
       </c>
       <c r="C521" s="33">
-        <v>1.2709999999999999</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="D521" s="34">
         <v>2.2000000000000002</v>
@@ -40293,10 +40293,10 @@
         <v>-1.23</v>
       </c>
       <c r="G521" s="33">
-        <v>1.071</v>
+        <v>1.073</v>
       </c>
       <c r="H521" s="33">
-        <v>-0.92900000000000005</v>
+        <v>-0.92700000000000005</v>
       </c>
       <c r="I521" s="33">
         <v>1.1379999999999999</v>
@@ -40308,7 +40308,7 @@
         <v>-530</v>
       </c>
       <c r="L521" s="35">
-        <v>-229</v>
+        <v>-227</v>
       </c>
       <c r="M521" s="32">
         <v>-162</v>
@@ -40323,7 +40323,7 @@
         <v>509</v>
       </c>
       <c r="C522" s="33">
-        <v>1.2609999999999999</v>
+        <v>1.264</v>
       </c>
       <c r="D522" s="34">
         <v>2.2000000000000002</v>
@@ -40335,10 +40335,10 @@
         <v>-1.2370000000000001</v>
       </c>
       <c r="G522" s="33">
-        <v>1.0609999999999999</v>
+        <v>1.0640000000000001</v>
       </c>
       <c r="H522" s="33">
-        <v>-0.93899999999999995</v>
+        <v>-0.93600000000000005</v>
       </c>
       <c r="I522" s="33">
         <v>1.1319999999999999</v>
@@ -40350,7 +40350,7 @@
         <v>-537</v>
       </c>
       <c r="L522" s="35">
-        <v>-239</v>
+        <v>-236</v>
       </c>
       <c r="M522" s="32">
         <v>-168</v>
@@ -40365,7 +40365,7 @@
         <v>510</v>
       </c>
       <c r="C523" s="33">
-        <v>1.2509999999999999</v>
+        <v>1.2549999999999999</v>
       </c>
       <c r="D523" s="34">
         <v>2.2000000000000002</v>
@@ -40377,10 +40377,10 @@
         <v>-1.244</v>
       </c>
       <c r="G523" s="33">
-        <v>1.0509999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="H523" s="33">
-        <v>-0.94899999999999995</v>
+        <v>-0.94499999999999995</v>
       </c>
       <c r="I523" s="33">
         <v>1.1259999999999999</v>
@@ -40392,7 +40392,7 @@
         <v>-544</v>
       </c>
       <c r="L523" s="35">
-        <v>-249</v>
+        <v>-245</v>
       </c>
       <c r="M523" s="32">
         <v>-174</v>
@@ -40407,7 +40407,7 @@
         <v>511</v>
       </c>
       <c r="C524" s="33">
-        <v>1.2410000000000001</v>
+        <v>1.246</v>
       </c>
       <c r="D524" s="34">
         <v>2.2000000000000002</v>
@@ -40419,10 +40419,10 @@
         <v>-1.2509999999999999</v>
       </c>
       <c r="G524" s="33">
-        <v>1.0409999999999999</v>
+        <v>1.046</v>
       </c>
       <c r="H524" s="33">
-        <v>-0.95899999999999996</v>
+        <v>-0.95399999999999996</v>
       </c>
       <c r="I524" s="33">
         <v>1.1200000000000001</v>
@@ -40434,7 +40434,7 @@
         <v>-551</v>
       </c>
       <c r="L524" s="35">
-        <v>-259</v>
+        <v>-254</v>
       </c>
       <c r="M524" s="32">
         <v>-180</v>
@@ -40449,7 +40449,7 @@
         <v>512</v>
       </c>
       <c r="C525" s="33">
-        <v>1.2310000000000001</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="D525" s="34">
         <v>2.2000000000000002</v>
@@ -40461,10 +40461,10 @@
         <v>-1.258</v>
       </c>
       <c r="G525" s="33">
-        <v>1.0309999999999999</v>
+        <v>1.0369999999999999</v>
       </c>
       <c r="H525" s="33">
-        <v>-0.96899999999999997</v>
+        <v>-0.96299999999999997</v>
       </c>
       <c r="I525" s="33">
         <v>1.1140000000000001</v>
@@ -40476,7 +40476,7 @@
         <v>-558</v>
       </c>
       <c r="L525" s="35">
-        <v>-269</v>
+        <v>-263</v>
       </c>
       <c r="M525" s="32">
         <v>-186</v>
@@ -40491,7 +40491,7 @@
         <v>513</v>
       </c>
       <c r="C526" s="33">
-        <v>1.2210000000000001</v>
+        <v>1.228</v>
       </c>
       <c r="D526" s="34">
         <v>2.2000000000000002</v>
@@ -40503,10 +40503,10 @@
         <v>-1.2649999999999999</v>
       </c>
       <c r="G526" s="33">
-        <v>1.0209999999999999</v>
+        <v>1.028</v>
       </c>
       <c r="H526" s="33">
-        <v>-0.97899999999999998</v>
+        <v>-0.97199999999999998</v>
       </c>
       <c r="I526" s="33">
         <v>1.1080000000000001</v>
@@ -40518,7 +40518,7 @@
         <v>-565</v>
       </c>
       <c r="L526" s="35">
-        <v>-279</v>
+        <v>-272</v>
       </c>
       <c r="M526" s="32">
         <v>-192</v>
@@ -40533,7 +40533,7 @@
         <v>514</v>
       </c>
       <c r="C527" s="33">
-        <v>1.2110000000000001</v>
+        <v>1.2190000000000001</v>
       </c>
       <c r="D527" s="34">
         <v>2.2000000000000002</v>
@@ -40545,10 +40545,10 @@
         <v>-1.272</v>
       </c>
       <c r="G527" s="33">
-        <v>1.0109999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="H527" s="33">
-        <v>-0.98899999999999999</v>
+        <v>-0.98099999999999998</v>
       </c>
       <c r="I527" s="33">
         <v>1.1020000000000001</v>
@@ -40560,7 +40560,7 @@
         <v>-572</v>
       </c>
       <c r="L527" s="35">
-        <v>-289</v>
+        <v>-281</v>
       </c>
       <c r="M527" s="32">
         <v>-198</v>
@@ -40575,7 +40575,7 @@
         <v>515</v>
       </c>
       <c r="C528" s="33">
-        <v>1.2010000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="D528" s="34">
         <v>2.2000000000000002</v>
@@ -40587,10 +40587,10 @@
         <v>-1.2789999999999999</v>
       </c>
       <c r="G528" s="33">
-        <v>1.0009999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="H528" s="33">
-        <v>-0.999</v>
+        <v>-0.99</v>
       </c>
       <c r="I528" s="33">
         <v>1.0960000000000001</v>
@@ -40602,7 +40602,7 @@
         <v>-579</v>
       </c>
       <c r="L528" s="35">
-        <v>-299</v>
+        <v>-290</v>
       </c>
       <c r="M528" s="32">
         <v>-204</v>
@@ -40617,7 +40617,7 @@
         <v>516</v>
       </c>
       <c r="C529" s="33">
-        <v>1.1910000000000001</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="D529" s="34">
         <v>2.2000000000000002</v>
@@ -40629,10 +40629,10 @@
         <v>-1.286</v>
       </c>
       <c r="G529" s="33">
-        <v>0.99099999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="H529" s="33">
-        <v>-1.0089999999999999</v>
+        <v>-0.999</v>
       </c>
       <c r="I529" s="33">
         <v>1.0900000000000001</v>
@@ -40644,7 +40644,7 @@
         <v>-586</v>
       </c>
       <c r="L529" s="35">
-        <v>-309</v>
+        <v>-299</v>
       </c>
       <c r="M529" s="32">
         <v>-210</v>
@@ -40659,7 +40659,7 @@
         <v>517</v>
       </c>
       <c r="C530" s="33">
-        <v>1.181</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="D530" s="34">
         <v>2.2000000000000002</v>
@@ -40671,10 +40671,10 @@
         <v>-1.2929999999999999</v>
       </c>
       <c r="G530" s="33">
-        <v>0.98099999999999998</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="H530" s="33">
-        <v>-1.0189999999999999</v>
+        <v>-1.008</v>
       </c>
       <c r="I530" s="33">
         <v>1.0840000000000001</v>
@@ -40686,7 +40686,7 @@
         <v>-593</v>
       </c>
       <c r="L530" s="35">
-        <v>-319</v>
+        <v>-308</v>
       </c>
       <c r="M530" s="32">
         <v>-216</v>
@@ -40701,7 +40701,7 @@
         <v>518</v>
       </c>
       <c r="C531" s="33">
-        <v>1.171</v>
+        <v>1.1830000000000001</v>
       </c>
       <c r="D531" s="34">
         <v>2.2000000000000002</v>
@@ -40713,10 +40713,10 @@
         <v>-1.3</v>
       </c>
       <c r="G531" s="33">
-        <v>0.97099999999999997</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="H531" s="33">
-        <v>-1.0289999999999999</v>
+        <v>-1.0169999999999999</v>
       </c>
       <c r="I531" s="33">
         <v>1.0780000000000001</v>
@@ -40728,7 +40728,7 @@
         <v>-600</v>
       </c>
       <c r="L531" s="35">
-        <v>-329</v>
+        <v>-317</v>
       </c>
       <c r="M531" s="32">
         <v>-222</v>
@@ -40743,7 +40743,7 @@
         <v>519</v>
       </c>
       <c r="C532" s="33">
-        <v>1.161</v>
+        <v>1.1739999999999999</v>
       </c>
       <c r="D532" s="34">
         <v>2.2000000000000002</v>
@@ -40755,10 +40755,10 @@
         <v>-1.3069999999999999</v>
       </c>
       <c r="G532" s="33">
-        <v>0.96099999999999997</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="H532" s="33">
-        <v>-1.0389999999999999</v>
+        <v>-1.026</v>
       </c>
       <c r="I532" s="33">
         <v>1.0720000000000001</v>
@@ -40770,7 +40770,7 @@
         <v>-607</v>
       </c>
       <c r="L532" s="35">
-        <v>-339</v>
+        <v>-326</v>
       </c>
       <c r="M532" s="32">
         <v>-228</v>
@@ -40785,7 +40785,7 @@
         <v>520</v>
       </c>
       <c r="C533" s="33">
-        <v>1.151</v>
+        <v>1.165</v>
       </c>
       <c r="D533" s="34">
         <v>2.2000000000000002</v>
@@ -40797,10 +40797,10 @@
         <v>-1.3140000000000001</v>
       </c>
       <c r="G533" s="33">
-        <v>0.95099999999999996</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="H533" s="33">
-        <v>-1.0489999999999999</v>
+        <v>-1.0349999999999999</v>
       </c>
       <c r="I533" s="33">
         <v>1.0660000000000001</v>
@@ -40812,7 +40812,7 @@
         <v>-614</v>
       </c>
       <c r="L533" s="35">
-        <v>-349</v>
+        <v>-335</v>
       </c>
       <c r="M533" s="32">
         <v>-234</v>
@@ -40827,7 +40827,7 @@
         <v>521</v>
       </c>
       <c r="C534" s="33">
-        <v>1.141</v>
+        <v>1.1559999999999999</v>
       </c>
       <c r="D534" s="34">
         <v>2.2000000000000002</v>
@@ -40839,10 +40839,10 @@
         <v>-1.321</v>
       </c>
       <c r="G534" s="33">
-        <v>0.94099999999999995</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="H534" s="33">
-        <v>-1.0589999999999999</v>
+        <v>-1.044</v>
       </c>
       <c r="I534" s="33">
         <v>1.06</v>
@@ -40854,7 +40854,7 @@
         <v>-621</v>
       </c>
       <c r="L534" s="35">
-        <v>-359</v>
+        <v>-344</v>
       </c>
       <c r="M534" s="32">
         <v>-240</v>
@@ -40869,7 +40869,7 @@
         <v>522</v>
       </c>
       <c r="C535" s="33">
-        <v>1.131</v>
+        <v>1.147</v>
       </c>
       <c r="D535" s="34">
         <v>2.2000000000000002</v>
@@ -40881,10 +40881,10 @@
         <v>-1.3280000000000001</v>
       </c>
       <c r="G535" s="33">
-        <v>0.93100000000000005</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="H535" s="33">
-        <v>-1.069</v>
+        <v>-1.0529999999999999</v>
       </c>
       <c r="I535" s="33">
         <v>1.054</v>
@@ -40896,7 +40896,7 @@
         <v>-628</v>
       </c>
       <c r="L535" s="35">
-        <v>-369</v>
+        <v>-353</v>
       </c>
       <c r="M535" s="32">
         <v>-246</v>
@@ -40911,7 +40911,7 @@
         <v>523</v>
       </c>
       <c r="C536" s="33">
-        <v>1.121</v>
+        <v>1.1379999999999999</v>
       </c>
       <c r="D536" s="34">
         <v>2.2000000000000002</v>
@@ -40923,10 +40923,10 @@
         <v>-1.335</v>
       </c>
       <c r="G536" s="33">
-        <v>0.92100000000000004</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="H536" s="33">
-        <v>-1.079</v>
+        <v>-1.0620000000000001</v>
       </c>
       <c r="I536" s="33">
         <v>1.048</v>
@@ -40938,7 +40938,7 @@
         <v>-635</v>
       </c>
       <c r="L536" s="35">
-        <v>-379</v>
+        <v>-362</v>
       </c>
       <c r="M536" s="32">
         <v>-252</v>
@@ -40953,7 +40953,7 @@
         <v>524</v>
       </c>
       <c r="C537" s="33">
-        <v>1.111</v>
+        <v>1.129</v>
       </c>
       <c r="D537" s="34">
         <v>2.2000000000000002</v>
@@ -40965,10 +40965,10 @@
         <v>-1.3420000000000001</v>
       </c>
       <c r="G537" s="33">
-        <v>0.91100000000000003</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H537" s="33">
-        <v>-1.089</v>
+        <v>-1.071</v>
       </c>
       <c r="I537" s="33">
         <v>1.042</v>
@@ -40980,7 +40980,7 @@
         <v>-642</v>
       </c>
       <c r="L537" s="35">
-        <v>-389</v>
+        <v>-371</v>
       </c>
       <c r="M537" s="32">
         <v>-258</v>
@@ -40995,7 +40995,7 @@
         <v>525</v>
       </c>
       <c r="C538" s="33">
-        <v>1.101</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D538" s="34">
         <v>2.2000000000000002</v>
@@ -41007,10 +41007,10 @@
         <v>-1.349</v>
       </c>
       <c r="G538" s="33">
-        <v>0.90100000000000002</v>
+        <v>0.92</v>
       </c>
       <c r="H538" s="33">
-        <v>-1.099</v>
+        <v>-1.08</v>
       </c>
       <c r="I538" s="33">
         <v>1.036</v>
@@ -41022,7 +41022,7 @@
         <v>-649</v>
       </c>
       <c r="L538" s="35">
-        <v>-399</v>
+        <v>-380</v>
       </c>
       <c r="M538" s="32">
         <v>-264</v>
@@ -41037,7 +41037,7 @@
         <v>526</v>
       </c>
       <c r="C539" s="33">
-        <v>1.091</v>
+        <v>1.111</v>
       </c>
       <c r="D539" s="34">
         <v>2.2000000000000002</v>
@@ -41049,10 +41049,10 @@
         <v>-1.3560000000000001</v>
       </c>
       <c r="G539" s="33">
-        <v>0.89100000000000001</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="H539" s="33">
-        <v>-1.109</v>
+        <v>-1.089</v>
       </c>
       <c r="I539" s="33">
         <v>1.03</v>
@@ -41064,7 +41064,7 @@
         <v>-656</v>
       </c>
       <c r="L539" s="35">
-        <v>-409</v>
+        <v>-389</v>
       </c>
       <c r="M539" s="32">
         <v>-270</v>
@@ -41079,7 +41079,7 @@
         <v>527</v>
       </c>
       <c r="C540" s="33">
-        <v>1.081</v>
+        <v>1.1020000000000001</v>
       </c>
       <c r="D540" s="34">
         <v>2.2000000000000002</v>
@@ -41091,10 +41091,10 @@
         <v>-1.363</v>
       </c>
       <c r="G540" s="33">
-        <v>0.88100000000000001</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="H540" s="33">
-        <v>-1.119</v>
+        <v>-1.0980000000000001</v>
       </c>
       <c r="I540" s="33">
         <v>1.024</v>
@@ -41106,7 +41106,7 @@
         <v>-663</v>
       </c>
       <c r="L540" s="35">
-        <v>-419</v>
+        <v>-398</v>
       </c>
       <c r="M540" s="32">
         <v>-276</v>
@@ -41121,7 +41121,7 @@
         <v>528</v>
       </c>
       <c r="C541" s="33">
-        <v>1.071</v>
+        <v>1.093</v>
       </c>
       <c r="D541" s="34">
         <v>2.2000000000000002</v>
@@ -41133,10 +41133,10 @@
         <v>-1.37</v>
       </c>
       <c r="G541" s="33">
-        <v>0.871</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="H541" s="33">
-        <v>-1.129</v>
+        <v>-1.107</v>
       </c>
       <c r="I541" s="33">
         <v>1.018</v>
@@ -41148,7 +41148,7 @@
         <v>-670</v>
       </c>
       <c r="L541" s="35">
-        <v>-429</v>
+        <v>-407</v>
       </c>
       <c r="M541" s="32">
         <v>-282</v>
@@ -41163,7 +41163,7 @@
         <v>529</v>
       </c>
       <c r="C542" s="33">
-        <v>1.0609999999999999</v>
+        <v>1.0840000000000001</v>
       </c>
       <c r="D542" s="34">
         <v>2.2000000000000002</v>
@@ -41175,10 +41175,10 @@
         <v>-1.377</v>
       </c>
       <c r="G542" s="33">
-        <v>0.86099999999999999</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="H542" s="33">
-        <v>-1.139</v>
+        <v>-1.1160000000000001</v>
       </c>
       <c r="I542" s="33">
         <v>1.012</v>
@@ -41190,7 +41190,7 @@
         <v>-677</v>
       </c>
       <c r="L542" s="35">
-        <v>-439</v>
+        <v>-416</v>
       </c>
       <c r="M542" s="32">
         <v>-288</v>
@@ -41205,7 +41205,7 @@
         <v>530</v>
       </c>
       <c r="C543" s="33">
-        <v>1.0509999999999999</v>
+        <v>1.075</v>
       </c>
       <c r="D543" s="34">
         <v>2.2000000000000002</v>
@@ -41217,10 +41217,10 @@
         <v>-1.3839999999999999</v>
       </c>
       <c r="G543" s="33">
-        <v>0.85099999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="H543" s="33">
-        <v>-1.149</v>
+        <v>-1.125</v>
       </c>
       <c r="I543" s="33">
         <v>1.006</v>
@@ -41232,7 +41232,7 @@
         <v>-684</v>
       </c>
       <c r="L543" s="35">
-        <v>-449</v>
+        <v>-425</v>
       </c>
       <c r="M543" s="32">
         <v>-294</v>
@@ -41247,7 +41247,7 @@
         <v>531</v>
       </c>
       <c r="C544" s="33">
-        <v>1.0409999999999999</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="D544" s="34">
         <v>2.2000000000000002</v>
@@ -41259,10 +41259,10 @@
         <v>-1.391</v>
       </c>
       <c r="G544" s="33">
-        <v>0.84099999999999997</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="H544" s="33">
-        <v>-1.159</v>
+        <v>-1.1339999999999999</v>
       </c>
       <c r="I544" s="33">
         <v>1</v>
@@ -41274,7 +41274,7 @@
         <v>-691</v>
       </c>
       <c r="L544" s="35">
-        <v>-459</v>
+        <v>-434</v>
       </c>
       <c r="M544" s="32">
         <v>-300</v>
@@ -41289,7 +41289,7 @@
         <v>532</v>
       </c>
       <c r="C545" s="33">
-        <v>1.0309999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
       <c r="D545" s="34">
         <v>2.2000000000000002</v>
@@ -41301,10 +41301,10 @@
         <v>-1.3979999999999999</v>
       </c>
       <c r="G545" s="33">
-        <v>0.83099999999999996</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="H545" s="33">
-        <v>-1.169</v>
+        <v>-1.143</v>
       </c>
       <c r="I545" s="33">
         <v>0.99399999999999999</v>
@@ -41316,7 +41316,7 @@
         <v>-698</v>
       </c>
       <c r="L545" s="35">
-        <v>-469</v>
+        <v>-443</v>
       </c>
       <c r="M545" s="32">
         <v>-306</v>
@@ -41331,7 +41331,7 @@
         <v>533</v>
       </c>
       <c r="C546" s="33">
-        <v>1.0209999999999999</v>
+        <v>1.048</v>
       </c>
       <c r="D546" s="34">
         <v>2.2000000000000002</v>
@@ -41343,10 +41343,10 @@
         <v>-1.405</v>
       </c>
       <c r="G546" s="33">
-        <v>0.82099999999999995</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="H546" s="33">
-        <v>-1.179</v>
+        <v>-1.1519999999999999</v>
       </c>
       <c r="I546" s="33">
         <v>0.98799999999999999</v>
@@ -41358,7 +41358,7 @@
         <v>-705</v>
       </c>
       <c r="L546" s="35">
-        <v>-479</v>
+        <v>-452</v>
       </c>
       <c r="M546" s="32">
         <v>-312</v>
@@ -41373,7 +41373,7 @@
         <v>534</v>
       </c>
       <c r="C547" s="33">
-        <v>1.0109999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="D547" s="34">
         <v>2.2000000000000002</v>
@@ -41385,10 +41385,10 @@
         <v>-1.4119999999999999</v>
       </c>
       <c r="G547" s="33">
-        <v>0.81100000000000005</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="H547" s="33">
-        <v>-1.1890000000000001</v>
+        <v>-1.161</v>
       </c>
       <c r="I547" s="33">
         <v>0.98199999999999998</v>
@@ -41400,7 +41400,7 @@
         <v>-712</v>
       </c>
       <c r="L547" s="35">
-        <v>-489</v>
+        <v>-461</v>
       </c>
       <c r="M547" s="32">
         <v>-318</v>
@@ -41415,7 +41415,7 @@
         <v>535</v>
       </c>
       <c r="C548" s="33">
-        <v>1.0009999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="D548" s="34">
         <v>2.2000000000000002</v>
@@ -41427,10 +41427,10 @@
         <v>-1.419</v>
       </c>
       <c r="G548" s="33">
-        <v>0.80100000000000005</v>
+        <v>0.83</v>
       </c>
       <c r="H548" s="33">
-        <v>-1.1990000000000001</v>
+        <v>-1.17</v>
       </c>
       <c r="I548" s="33">
         <v>0.97599999999999998</v>
@@ -41442,7 +41442,7 @@
         <v>-719</v>
       </c>
       <c r="L548" s="35">
-        <v>-499</v>
+        <v>-470</v>
       </c>
       <c r="M548" s="32">
         <v>-324</v>
@@ -41457,7 +41457,7 @@
         <v>536</v>
       </c>
       <c r="C549" s="33">
-        <v>0.99099999999999999</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="D549" s="34">
         <v>2.2000000000000002</v>
@@ -41469,10 +41469,10 @@
         <v>-1.4259999999999999</v>
       </c>
       <c r="G549" s="33">
-        <v>0.79100000000000004</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="H549" s="33">
-        <v>-1.2090000000000001</v>
+        <v>-1.179</v>
       </c>
       <c r="I549" s="33">
         <v>0.97</v>
@@ -41484,7 +41484,7 @@
         <v>-726</v>
       </c>
       <c r="L549" s="35">
-        <v>-509</v>
+        <v>-479</v>
       </c>
       <c r="M549" s="32">
         <v>-330</v>
@@ -41499,7 +41499,7 @@
         <v>537</v>
       </c>
       <c r="C550" s="33">
-        <v>0.98099999999999998</v>
+        <v>1.012</v>
       </c>
       <c r="D550" s="34">
         <v>2.2000000000000002</v>
@@ -41511,10 +41511,10 @@
         <v>-1.4330000000000001</v>
       </c>
       <c r="G550" s="33">
-        <v>0.78100000000000003</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="H550" s="33">
-        <v>-1.2190000000000001</v>
+        <v>-1.1879999999999999</v>
       </c>
       <c r="I550" s="33">
         <v>0.96399999999999997</v>
@@ -41526,7 +41526,7 @@
         <v>-733</v>
       </c>
       <c r="L550" s="35">
-        <v>-519</v>
+        <v>-488</v>
       </c>
       <c r="M550" s="32">
         <v>-336</v>
@@ -41541,7 +41541,7 @@
         <v>538</v>
       </c>
       <c r="C551" s="33">
-        <v>0.97099999999999997</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="D551" s="34">
         <v>2.2000000000000002</v>
@@ -41553,10 +41553,10 @@
         <v>-1.44</v>
       </c>
       <c r="G551" s="33">
-        <v>0.77100000000000002</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="H551" s="33">
-        <v>-1.2290000000000001</v>
+        <v>-1.1970000000000001</v>
       </c>
       <c r="I551" s="33">
         <v>0.95799999999999996</v>
@@ -41568,7 +41568,7 @@
         <v>-740</v>
       </c>
       <c r="L551" s="35">
-        <v>-529</v>
+        <v>-497</v>
       </c>
       <c r="M551" s="32">
         <v>-342</v>
@@ -41583,7 +41583,7 @@
         <v>539</v>
       </c>
       <c r="C552" s="33">
-        <v>0.96099999999999997</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="D552" s="34">
         <v>2.2000000000000002</v>
@@ -41595,10 +41595,10 @@
         <v>-1.4470000000000001</v>
       </c>
       <c r="G552" s="33">
-        <v>0.76100000000000001</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="H552" s="33">
-        <v>-1.2390000000000001</v>
+        <v>-1.206</v>
       </c>
       <c r="I552" s="33">
         <v>0.95199999999999996</v>
@@ -41610,7 +41610,7 @@
         <v>-747</v>
       </c>
       <c r="L552" s="35">
-        <v>-539</v>
+        <v>-506</v>
       </c>
       <c r="M552" s="32">
         <v>-348</v>
@@ -41625,7 +41625,7 @@
         <v>540</v>
       </c>
       <c r="C553" s="33">
-        <v>0.95099999999999996</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D553" s="34">
         <v>2.2000000000000002</v>
@@ -41637,10 +41637,10 @@
         <v>-1.454</v>
       </c>
       <c r="G553" s="33">
-        <v>0.751</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="H553" s="33">
-        <v>-1.2490000000000001</v>
+        <v>-1.2150000000000001</v>
       </c>
       <c r="I553" s="33">
         <v>0.94599999999999995</v>
@@ -41652,7 +41652,7 @@
         <v>-754</v>
       </c>
       <c r="L553" s="35">
-        <v>-549</v>
+        <v>-515</v>
       </c>
       <c r="M553" s="32">
         <v>-354</v>
@@ -41667,7 +41667,7 @@
         <v>541</v>
       </c>
       <c r="C554" s="33">
-        <v>0.94099999999999995</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D554" s="34">
         <v>2.2000000000000002</v>
@@ -41679,10 +41679,10 @@
         <v>-1.4610000000000001</v>
       </c>
       <c r="G554" s="33">
-        <v>0.74099999999999999</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="H554" s="33">
-        <v>-1.2589999999999999</v>
+        <v>-1.224</v>
       </c>
       <c r="I554" s="33">
         <v>0.94</v>
@@ -41694,7 +41694,7 @@
         <v>-761</v>
       </c>
       <c r="L554" s="35">
-        <v>-559</v>
+        <v>-524</v>
       </c>
       <c r="M554" s="32">
         <v>-360</v>
@@ -41709,7 +41709,7 @@
         <v>542</v>
       </c>
       <c r="C555" s="33">
-        <v>0.93100000000000005</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="D555" s="34">
         <v>2.2000000000000002</v>
@@ -41721,10 +41721,10 @@
         <v>-1.468</v>
       </c>
       <c r="G555" s="33">
-        <v>0.73099999999999998</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="H555" s="33">
-        <v>-1.2689999999999999</v>
+        <v>-1.2330000000000001</v>
       </c>
       <c r="I555" s="33">
         <v>0.93400000000000005</v>
@@ -41736,7 +41736,7 @@
         <v>-768</v>
       </c>
       <c r="L555" s="35">
-        <v>-569</v>
+        <v>-533</v>
       </c>
       <c r="M555" s="32">
         <v>-366</v>
@@ -41751,7 +41751,7 @@
         <v>543</v>
       </c>
       <c r="C556" s="33">
-        <v>0.92100000000000004</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="D556" s="34">
         <v>2.2000000000000002</v>
@@ -41763,10 +41763,10 @@
         <v>-1.4750000000000001</v>
       </c>
       <c r="G556" s="33">
-        <v>0.72099999999999997</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="H556" s="33">
-        <v>-1.2789999999999999</v>
+        <v>-1.242</v>
       </c>
       <c r="I556" s="33">
         <v>0.92800000000000005</v>
@@ -41778,7 +41778,7 @@
         <v>-775</v>
       </c>
       <c r="L556" s="35">
-        <v>-579</v>
+        <v>-542</v>
       </c>
       <c r="M556" s="32">
         <v>-372</v>
@@ -41793,7 +41793,7 @@
         <v>544</v>
       </c>
       <c r="C557" s="33">
-        <v>0.91200000000000003</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="D557" s="34">
         <v>2.2000000000000002</v>
@@ -41805,10 +41805,10 @@
         <v>-1.482</v>
       </c>
       <c r="G557" s="33">
-        <v>0.71199999999999997</v>
+        <v>0.749</v>
       </c>
       <c r="H557" s="33">
-        <v>-1.288</v>
+        <v>-1.2509999999999999</v>
       </c>
       <c r="I557" s="33">
         <v>0.92200000000000004</v>
@@ -41820,7 +41820,7 @@
         <v>-782</v>
       </c>
       <c r="L557" s="35">
-        <v>-588</v>
+        <v>-551</v>
       </c>
       <c r="M557" s="32">
         <v>-378</v>
@@ -41835,7 +41835,7 @@
         <v>545</v>
       </c>
       <c r="C558" s="33">
-        <v>0.90300000000000002</v>
+        <v>0.94</v>
       </c>
       <c r="D558" s="34">
         <v>2.2000000000000002</v>
@@ -41847,10 +41847,10 @@
         <v>-1.4890000000000001</v>
       </c>
       <c r="G558" s="33">
-        <v>0.70299999999999996</v>
+        <v>0.74</v>
       </c>
       <c r="H558" s="33">
-        <v>-1.2969999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="I558" s="33">
         <v>0.91600000000000004</v>
@@ -41862,7 +41862,7 @@
         <v>-789</v>
       </c>
       <c r="L558" s="35">
-        <v>-597</v>
+        <v>-560</v>
       </c>
       <c r="M558" s="32">
         <v>-384</v>
@@ -41877,7 +41877,7 @@
         <v>546</v>
       </c>
       <c r="C559" s="33">
-        <v>0.89400000000000002</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="D559" s="34">
         <v>2.2000000000000002</v>
@@ -41889,10 +41889,10 @@
         <v>-1.496</v>
       </c>
       <c r="G559" s="33">
-        <v>0.69399999999999995</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="H559" s="33">
-        <v>-1.306</v>
+        <v>-1.2689999999999999</v>
       </c>
       <c r="I559" s="33">
         <v>0.91</v>
@@ -41904,7 +41904,7 @@
         <v>-796</v>
       </c>
       <c r="L559" s="35">
-        <v>-606</v>
+        <v>-569</v>
       </c>
       <c r="M559" s="32">
         <v>-390</v>
@@ -41919,7 +41919,7 @@
         <v>547</v>
       </c>
       <c r="C560" s="33">
-        <v>0.88500000000000001</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="D560" s="34">
         <v>2.2000000000000002</v>
@@ -41931,10 +41931,10 @@
         <v>-1.5029999999999999</v>
       </c>
       <c r="G560" s="33">
-        <v>0.68500000000000005</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="H560" s="33">
-        <v>-1.3149999999999999</v>
+        <v>-1.278</v>
       </c>
       <c r="I560" s="33">
         <v>0.90400000000000003</v>
@@ -41946,7 +41946,7 @@
         <v>-803</v>
       </c>
       <c r="L560" s="35">
-        <v>-615</v>
+        <v>-578</v>
       </c>
       <c r="M560" s="32">
         <v>-396</v>
@@ -41961,7 +41961,7 @@
         <v>548</v>
       </c>
       <c r="C561" s="33">
-        <v>0.876</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="D561" s="34">
         <v>2.2000000000000002</v>
@@ -41973,10 +41973,10 @@
         <v>-1.51</v>
       </c>
       <c r="G561" s="33">
-        <v>0.67600000000000005</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="H561" s="33">
-        <v>-1.3240000000000001</v>
+        <v>-1.2869999999999999</v>
       </c>
       <c r="I561" s="33">
         <v>0.89800000000000002</v>
@@ -41988,7 +41988,7 @@
         <v>-810</v>
       </c>
       <c r="L561" s="35">
-        <v>-624</v>
+        <v>-587</v>
       </c>
       <c r="M561" s="32">
         <v>-402</v>
@@ -42003,7 +42003,7 @@
         <v>549</v>
       </c>
       <c r="C562" s="33">
-        <v>0.86799999999999999</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="D562" s="34">
         <v>2.2000000000000002</v>
@@ -42015,10 +42015,10 @@
         <v>-1.5169999999999999</v>
       </c>
       <c r="G562" s="33">
-        <v>0.66800000000000004</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="H562" s="33">
-        <v>-1.3320000000000001</v>
+        <v>-1.2969999999999999</v>
       </c>
       <c r="I562" s="33">
         <v>0.89200000000000002</v>
@@ -42030,7 +42030,7 @@
         <v>-817</v>
       </c>
       <c r="L562" s="35">
-        <v>-632</v>
+        <v>-597</v>
       </c>
       <c r="M562" s="32">
         <v>-408</v>
@@ -42045,7 +42045,7 @@
         <v>550</v>
       </c>
       <c r="C563" s="33">
-        <v>0.86</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="D563" s="34">
         <v>2.2000000000000002</v>
@@ -42057,10 +42057,10 @@
         <v>-1.524</v>
       </c>
       <c r="G563" s="33">
-        <v>0.66</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="H563" s="33">
-        <v>-1.34</v>
+        <v>-1.3069999999999999</v>
       </c>
       <c r="I563" s="33">
         <v>0.88600000000000001</v>
@@ -42072,7 +42072,7 @@
         <v>-824</v>
       </c>
       <c r="L563" s="35">
-        <v>-640</v>
+        <v>-607</v>
       </c>
       <c r="M563" s="32">
         <v>-414</v>
@@ -42087,7 +42087,7 @@
         <v>551</v>
       </c>
       <c r="C564" s="33">
-        <v>0.85199999999999998</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="D564" s="34">
         <v>2.2000000000000002</v>
@@ -42099,10 +42099,10 @@
         <v>-1.5309999999999999</v>
       </c>
       <c r="G564" s="33">
-        <v>0.65200000000000002</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="H564" s="33">
-        <v>-1.3480000000000001</v>
+        <v>-1.3169999999999999</v>
       </c>
       <c r="I564" s="33">
         <v>0.88</v>
@@ -42114,7 +42114,7 @@
         <v>-831</v>
       </c>
       <c r="L564" s="35">
-        <v>-648</v>
+        <v>-617</v>
       </c>
       <c r="M564" s="32">
         <v>-420</v>
@@ -42129,7 +42129,7 @@
         <v>552</v>
       </c>
       <c r="C565" s="33">
-        <v>0.84399999999999997</v>
+        <v>0.873</v>
       </c>
       <c r="D565" s="34">
         <v>2.2000000000000002</v>
@@ -42141,10 +42141,10 @@
         <v>-1.538</v>
       </c>
       <c r="G565" s="33">
-        <v>0.64400000000000002</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="H565" s="33">
-        <v>-1.3560000000000001</v>
+        <v>-1.327</v>
       </c>
       <c r="I565" s="33">
         <v>0.874</v>
@@ -42156,7 +42156,7 @@
         <v>-838</v>
       </c>
       <c r="L565" s="35">
-        <v>-656</v>
+        <v>-627</v>
       </c>
       <c r="M565" s="32">
         <v>-426</v>
@@ -42171,7 +42171,7 @@
         <v>553</v>
       </c>
       <c r="C566" s="33">
-        <v>0.83599999999999997</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="D566" s="34">
         <v>2.2000000000000002</v>
@@ -42183,10 +42183,10 @@
         <v>-1.5449999999999999</v>
       </c>
       <c r="G566" s="33">
-        <v>0.63600000000000001</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="H566" s="33">
-        <v>-1.3640000000000001</v>
+        <v>-1.337</v>
       </c>
       <c r="I566" s="33">
         <v>0.86899999999999999</v>
@@ -42198,7 +42198,7 @@
         <v>-845</v>
       </c>
       <c r="L566" s="35">
-        <v>-664</v>
+        <v>-637</v>
       </c>
       <c r="M566" s="32">
         <v>-431</v>
@@ -42213,7 +42213,7 @@
         <v>554</v>
       </c>
       <c r="C567" s="33">
-        <v>0.82799999999999996</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="D567" s="34">
         <v>2.2000000000000002</v>
@@ -42225,10 +42225,10 @@
         <v>-1.5509999999999999</v>
       </c>
       <c r="G567" s="33">
-        <v>0.628</v>
+        <v>0.65300000000000002</v>
       </c>
       <c r="H567" s="33">
-        <v>-1.3720000000000001</v>
+        <v>-1.347</v>
       </c>
       <c r="I567" s="33">
         <v>0.86399999999999999</v>
@@ -42240,7 +42240,7 @@
         <v>-851</v>
       </c>
       <c r="L567" s="35">
-        <v>-672</v>
+        <v>-647</v>
       </c>
       <c r="M567" s="32">
         <v>-436</v>
@@ -42255,7 +42255,7 @@
         <v>555</v>
       </c>
       <c r="C568" s="33">
-        <v>0.82099999999999995</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="D568" s="34">
         <v>2.2000000000000002</v>
@@ -42267,10 +42267,10 @@
         <v>-1.5569999999999999</v>
       </c>
       <c r="G568" s="33">
-        <v>0.621</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="H568" s="33">
-        <v>-1.379</v>
+        <v>-1.3560000000000001</v>
       </c>
       <c r="I568" s="33">
         <v>0.85899999999999999</v>
@@ -42282,7 +42282,7 @@
         <v>-857</v>
       </c>
       <c r="L568" s="35">
-        <v>-679</v>
+        <v>-656</v>
       </c>
       <c r="M568" s="32">
         <v>-441</v>
@@ -42297,7 +42297,7 @@
         <v>556</v>
       </c>
       <c r="C569" s="33">
-        <v>0.81399999999999995</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="D569" s="34">
         <v>2.2000000000000002</v>
@@ -42309,25 +42309,25 @@
         <v>-1.5629999999999999</v>
       </c>
       <c r="G569" s="33">
-        <v>0.61399999999999999</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="H569" s="33">
-        <v>-1.3859999999999999</v>
+        <v>-1.365</v>
       </c>
       <c r="I569" s="33">
-        <v>0.85399999999999998</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="J569" s="33">
-        <v>-1.1459999999999999</v>
+        <v>-1.145</v>
       </c>
       <c r="K569" s="32">
         <v>-863</v>
       </c>
       <c r="L569" s="35">
-        <v>-686</v>
+        <v>-665</v>
       </c>
       <c r="M569" s="32">
-        <v>-446</v>
+        <v>-445</v>
       </c>
       <c r="N569" s="32"/>
     </row>
@@ -42339,7 +42339,7 @@
         <v>557</v>
       </c>
       <c r="C570" s="33">
-        <v>0.80800000000000005</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="D570" s="34">
         <v>2.2000000000000002</v>
@@ -42351,25 +42351,25 @@
         <v>-1.569</v>
       </c>
       <c r="G570" s="33">
-        <v>0.60799999999999998</v>
+        <v>0.626</v>
       </c>
       <c r="H570" s="33">
-        <v>-1.3919999999999999</v>
+        <v>-1.3740000000000001</v>
       </c>
       <c r="I570" s="33">
-        <v>0.84899999999999998</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="J570" s="33">
-        <v>-1.151</v>
+        <v>-1.149</v>
       </c>
       <c r="K570" s="32">
         <v>-869</v>
       </c>
       <c r="L570" s="35">
-        <v>-692</v>
+        <v>-674</v>
       </c>
       <c r="M570" s="32">
-        <v>-451</v>
+        <v>-449</v>
       </c>
       <c r="N570" s="32"/>
     </row>
@@ -42381,7 +42381,7 @@
         <v>558</v>
       </c>
       <c r="C571" s="33">
-        <v>0.80200000000000005</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="D571" s="34">
         <v>2.2000000000000002</v>
@@ -42393,25 +42393,25 @@
         <v>-1.5740000000000001</v>
       </c>
       <c r="G571" s="33">
-        <v>0.60199999999999998</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H571" s="33">
-        <v>-1.3979999999999999</v>
+        <v>-1.3819999999999999</v>
       </c>
       <c r="I571" s="33">
-        <v>0.84499999999999997</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="J571" s="33">
-        <v>-1.155</v>
+        <v>-1.153</v>
       </c>
       <c r="K571" s="32">
         <v>-874</v>
       </c>
       <c r="L571" s="35">
-        <v>-698</v>
+        <v>-682</v>
       </c>
       <c r="M571" s="32">
-        <v>-455</v>
+        <v>-453</v>
       </c>
       <c r="N571" s="32"/>
     </row>
@@ -42423,37 +42423,37 @@
         <v>559</v>
       </c>
       <c r="C572" s="33">
-        <v>0.79700000000000004</v>
+        <v>0.81</v>
       </c>
       <c r="D572" s="34">
         <v>2.2000000000000002</v>
       </c>
       <c r="E572" s="33">
-        <v>0.42</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F572" s="33">
-        <v>-1.58</v>
+        <v>-1.579</v>
       </c>
       <c r="G572" s="33">
-        <v>0.59699999999999998</v>
+        <v>0.61</v>
       </c>
       <c r="H572" s="33">
-        <v>-1.403</v>
+        <v>-1.39</v>
       </c>
       <c r="I572" s="33">
-        <v>0.84099999999999997</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="J572" s="33">
-        <v>-1.159</v>
+        <v>-1.1559999999999999</v>
       </c>
       <c r="K572" s="32">
-        <v>-880</v>
+        <v>-879</v>
       </c>
       <c r="L572" s="35">
-        <v>-703</v>
+        <v>-690</v>
       </c>
       <c r="M572" s="32">
-        <v>-459</v>
+        <v>-456</v>
       </c>
       <c r="N572" s="32"/>
     </row>
@@ -42465,37 +42465,37 @@
         <v>560</v>
       </c>
       <c r="C573" s="33">
-        <v>0.79300000000000004</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="D573" s="34">
         <v>2.2000000000000002</v>
       </c>
       <c r="E573" s="33">
-        <v>0.41499999999999998</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="F573" s="33">
-        <v>-1.585</v>
+        <v>-1.583</v>
       </c>
       <c r="G573" s="33">
-        <v>0.59299999999999997</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="H573" s="33">
-        <v>-1.407</v>
+        <v>-1.397</v>
       </c>
       <c r="I573" s="33">
-        <v>0.83899999999999997</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="J573" s="33">
-        <v>-1.161</v>
+        <v>-1.159</v>
       </c>
       <c r="K573" s="32">
-        <v>-885</v>
+        <v>-883</v>
       </c>
       <c r="L573" s="35">
-        <v>-707</v>
+        <v>-697</v>
       </c>
       <c r="M573" s="32">
-        <v>-461</v>
+        <v>-459</v>
       </c>
       <c r="N573" s="32"/>
     </row>
@@ -42507,37 +42507,37 @@
         <v>561</v>
       </c>
       <c r="C574" s="33">
-        <v>0.79</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="D574" s="34">
         <v>2.2000000000000002</v>
       </c>
       <c r="E574" s="33">
-        <v>0.41099999999999998</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="F574" s="33">
-        <v>-1.589</v>
+        <v>-1.587</v>
       </c>
       <c r="G574" s="33">
-        <v>0.59</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="H574" s="33">
-        <v>-1.41</v>
+        <v>-1.403</v>
       </c>
       <c r="I574" s="33">
-        <v>0.83799999999999997</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="J574" s="33">
-        <v>-1.1619999999999999</v>
+        <v>-1.161</v>
       </c>
       <c r="K574" s="32">
-        <v>-889</v>
+        <v>-887</v>
       </c>
       <c r="L574" s="35">
-        <v>-710</v>
+        <v>-703</v>
       </c>
       <c r="M574" s="32">
-        <v>-462</v>
+        <v>-461</v>
       </c>
       <c r="N574" s="32"/>
     </row>
@@ -42549,22 +42549,22 @@
         <v>562</v>
       </c>
       <c r="C575" s="33">
-        <v>0.78900000000000003</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="D575" s="34">
         <v>2.2000000000000002</v>
       </c>
       <c r="E575" s="33">
-        <v>0.40799999999999997</v>
+        <v>0.41</v>
       </c>
       <c r="F575" s="33">
-        <v>-1.5920000000000001</v>
+        <v>-1.59</v>
       </c>
       <c r="G575" s="33">
-        <v>0.58899999999999997</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="H575" s="33">
-        <v>-1.411</v>
+        <v>-1.4079999999999999</v>
       </c>
       <c r="I575" s="33">
         <v>0.83799999999999997</v>
@@ -42573,10 +42573,10 @@
         <v>-1.1619999999999999</v>
       </c>
       <c r="K575" s="32">
-        <v>-892</v>
+        <v>-890</v>
       </c>
       <c r="L575" s="35">
-        <v>-711</v>
+        <v>-708</v>
       </c>
       <c r="M575" s="32">
         <v>-462</v>
